--- a/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
+++ b/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
@@ -540,7 +540,11 @@
           <t>Что Питание даёт само по себе — новый брейншторм. Деньги со станций отклонены (24.09): источников денег и так слишком много, а иконографику для этого лаконично не вставить. Питание сейчас — свободная перекладка кубиков и больше ничего.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Решено 24.09 (к проверке на ботах). ПИТАНИЕ: операций столько, сколько источников (ЦУ + энергостанции на поле). Операция — либо «собрать»: стянуть кубики с потребителей на одну энергостанцию до её вместимости; либо «раздать»: с одной энергостанции разложить по потребителям сколько угодно её кубиков. Свободной перекладки больше нет. УРОН: кубик урона по зданию ложится в ячейку энергии, если есть куда; ячейка с уроном не запитана. ПОЧИНКА: кубик энергии, положенный в ячейку с уроном, снимает урон и сразу запитывает её — отдельной операции нет. Урон не в ячейке (сверх ячеек — у ЦУ 1 ячейка при прочности 3; на энергостанциях — ячеек нет; на войсках; от карт прочности) не лечится. Урон с энергостанции не снимается. Не решено: выбивает ли урон кубик из запитанной ячейки, если свободной нет (предложение — да, кубик уходит на источники владельца); правило «ЦУ запитано любым кубиком» заменить на «когда в его ячейке энергия».</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">

--- a/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
+++ b/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Решено 24.09 (к проверке на ботах). ПИТАНИЕ: операций столько, сколько источников (ЦУ + энергостанции на поле). Операция — либо «собрать»: стянуть кубики с потребителей на одну энергостанцию до её вместимости; либо «раздать»: с одной энергостанции разложить по потребителям сколько угодно её кубиков. Свободной перекладки больше нет. УРОН: кубик урона по зданию ложится в ячейку энергии, если есть куда; ячейка с уроном не запитана. ПОЧИНКА: кубик энергии, положенный в ячейку с уроном, снимает урон и сразу запитывает её — отдельной операции нет. Урон не в ячейке (сверх ячеек — у ЦУ 1 ячейка при прочности 3; на энергостанциях — ячеек нет; на войсках; от карт прочности) не лечится. Урон с энергостанции не снимается. Не решено: выбивает ли урон кубик из запитанной ячейки, если свободной нет (предложение — да, кубик уходит на источники владельца); правило «ЦУ запитано любым кубиком» заменить на «когда в его ячейке энергия».</t>
+          <t>Решено 24.09 (к проверке на ботах). ПИТАНИЕ: операций столько, сколько источников (ЦУ + энергостанции на поле). Операция — либо «собрать»: стянуть кубики с потребителей на одну энергостанцию до её вместимости; либо «раздать»: с одной энергостанции разложить по потребителям сколько угодно её кубиков. Свободной перекладки больше нет. УРОН: кубик урона по зданию ложится в ячейку энергии, пока на здании есть ячейки без урона. Если в ячейке лежал кубик энергии, он уходит на любой источник владельца по выбору владельца (как при уничтожении потребителя, гл. 6); какую ячейку занять, тоже выбирает владелец. Ячейка с уроном не запитана. ПОЧИНКА: кубик энергии, положенный в ячейку с уроном, снимает урон и сразу запитывает её — отдельной операции нет. Урон не в ячейке (сверх ячеек — у ЦУ 1 ячейка при прочности 3; на энергостанциях — ячеек нет; на войсках; от карт прочности) не лечится. Урон с энергостанции не снимается. Книгу поправить: правило «ЦУ запитано любым кубиком» заменить на «когда в его ячейке энергия».</t>
         </is>
       </c>
     </row>

--- a/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
+++ b/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Решено 24.09 (к проверке на ботах). ПИТАНИЕ: операций столько, сколько источников (ЦУ + энергостанции на поле). Операция — либо «собрать»: стянуть кубики с потребителей на одну энергостанцию до её вместимости; либо «раздать»: с одной энергостанции разложить по потребителям сколько угодно её кубиков. Свободной перекладки больше нет. УРОН: кубик урона по зданию ложится в ячейку энергии, пока на здании есть ячейки без урона. Если в ячейке лежал кубик энергии, он уходит на любой источник владельца по выбору владельца (как при уничтожении потребителя, гл. 6); какую ячейку занять, тоже выбирает владелец. Ячейка с уроном не запитана. ПОЧИНКА: кубик энергии, положенный в ячейку с уроном, снимает урон и сразу запитывает её — отдельной операции нет. Урон не в ячейке (сверх ячеек — у ЦУ 1 ячейка при прочности 3; на энергостанциях — ячеек нет; на войсках; от карт прочности) не лечится. Урон с энергостанции не снимается. Книгу поправить: правило «ЦУ запитано любым кубиком» заменить на «когда в его ячейке энергия».</t>
+          <t>Решено 24.09 (к проверке на ботах). ПИТАНИЕ: операций столько, сколько источников (ЦУ + энергостанции на поле). Операция — либо «собрать»: стянуть кубики с потребителей на одну энергостанцию до её вместимости; либо «раздать»: с одной энергостанции разложить по потребителям сколько угодно её кубиков. Свободной перекладки больше нет. УРОН: кубик урона по зданию ложится в ячейку энергии, пока на здании есть ячейки без урона. Если в ячейке лежал кубик энергии, он уходит на любой источник владельца по выбору владельца (как при уничтожении потребителя, гл. 6). Ячейка с уроном не запитана. ПОЧИНКА: кубик энергии, положенный в ячейку с уроном, снимает урон и сразу запитывает её — отдельной операции нет. Урон не в ячейке (сверх ячеек — у ЦУ 1 ячейка при прочности 3; на энергостанциях — ячеек нет; на войсках; от карт прочности) не лечится. Урон с энергостанции не снимается. Книгу поправить: правило «ЦУ запитано любым кубиком» заменить на «когда в его ячейке энергия».</t>
         </is>
       </c>
     </row>

--- a/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
+++ b/docs/ОТКРЫТЫЕ ВОПРОСЫ — для ответов (24.09.2026).xlsx
@@ -586,7 +586,11 @@
           <t>Кубик энергии на жетоне войска. Положить можно, сам по себе ничего не даёт; силу дают две карты арсенала (+1 к скорости, +1 к прочности). Нужны точные формулировки карт: цена, что с кубиком после удара и после хода.</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr"/>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Предложение 24.09 (к утверждению). В книге правила нет — живёт только на двух картах арсенала с ОДНИМ названием «Боевое питание»: одноимённые карты вместе не ставятся, поэтому щит и форсаж у игрока не сойдутся. Щит: постоянно — в Питании можно раздавать энергию и на свои жетоны войск, не больше 1 кубика на жетон; атака по жетону с энергией вместо урона отправляет энергию на ваш источник. Форсаж: постоянно — то же право раздачи; жетон с энергией перемещается на 1 гекс дальше, после перемещения энергия уходит на ваш источник. Цены сверх карты нет: платишь операцией Питания и тем, что кубик не запитывает здание. Верхний эффект — подобрать. Правило «двух одноимённых арсеналов не бывает» внесено 24.09 в книгу (гл. 4) и в движок.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
